--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-01-2026.xlsx
@@ -1125,7 +1125,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£20.97</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>£23.32</t>
+          <t>£22.75</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£26.35</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£26.35</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£37.39</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£73.80</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.planetinsulation.co.uk/products/celotex-pir-tb-ga-xr?variant=42844828631277</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>£40.04</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/celotex-xr4130-high-performance-pir-insulation-2400-x-1200-x-130mm</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£853.62</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/celotex-pl4000-52-5mm</t>
+          <t>£31.63</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/525mm-celotex-pl4040-pir-insulated-plasterboard-2400mm-x-1200mm-525mm</t>
+          <t>£32.37</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>£31.65</t>
+          <t>£31.36</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>£35.60</t>
+          <t>£34.44</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>£40.48</t>
+          <t>£39.18</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£41.25</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£39.38</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£1057.71</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
